--- a/server/report_output/buildshop_admin_report.xlsx
+++ b/server/report_output/buildshop_admin_report.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дата формування: 21.04.2026 18:46</t>
+          <t>Дата формування: 21.04.2026 19:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/server/report_output/buildshop_admin_report.xlsx
+++ b/server/report_output/buildshop_admin_report.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дата формування: 21.04.2026 19:14</t>
+          <t>Дата формування: 21.04.2026 19:40</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/server/report_output/buildshop_admin_report.xlsx
+++ b/server/report_output/buildshop_admin_report.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дата формування: 21.04.2026 19:40</t>
+          <t>Дата формування: 21.04.2026 21:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
